--- a/data/trans_orig/IP24-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP24-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre en 2007 (tasa de respuesta: 99,76%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre en 2007 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16030</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17935</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>33156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>489</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>776</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24828</t>
+          <t>25079</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13161</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26166</t>
+          <t>25968</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28335</t>
+          <t>28109</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46281</t>
+          <t>46614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69793</t>
+          <t>69378</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84576</t>
+          <t>83945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76465</t>
+          <t>76652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92958</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149537</t>
+          <t>150690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172107</t>
+          <t>172855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,42%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>14998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13002</t>
+          <t>13195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11683</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>24760</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15457</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29545</t>
+          <t>30255</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,77 +1661,77 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>26250</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19208</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>33943</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>13,38%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>48243</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>37751</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>59354</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t>11,74%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>26250</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>19429</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>34643</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>13,65%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>48243</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>39015</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>60271</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>152367</t>
+          <t>153788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>177249</t>
+          <t>177839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145831</t>
+          <t>146849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171150</t>
+          <t>170391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>306307</t>
+          <t>308261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>342351</t>
+          <t>342213</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41821</t>
+          <t>40898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62951</t>
+          <t>62328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44163</t>
+          <t>44269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65144</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91041</t>
+          <t>91747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119990</t>
+          <t>120196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11600</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11207</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24223</t>
+          <t>23359</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16097</t>
+          <t>15955</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31195</t>
+          <t>31720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18117</t>
+          <t>18088</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32261</t>
+          <t>31903</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29135</t>
+          <t>29427</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45985</t>
+          <t>46128</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51699</t>
+          <t>51520</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73065</t>
+          <t>72629</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71156</t>
+          <t>72169</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89044</t>
+          <t>88410</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62588</t>
+          <t>63259</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81750</t>
+          <t>82519</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139814</t>
+          <t>140811</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>167170</t>
+          <t>165886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,8%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22156</t>
+          <t>22175</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19938</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37761</t>
+          <t>38069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18759</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31946</t>
+          <t>32531</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51108</t>
+          <t>50785</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41958</t>
+          <t>42272</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63724</t>
+          <t>63947</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36889</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55165</t>
+          <t>55073</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66674</t>
+          <t>65714</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>88211</t>
+          <t>87924</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>107444</t>
+          <t>108289</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>137823</t>
+          <t>137493</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>98692</t>
+          <t>97840</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>121501</t>
+          <t>120908</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62598</t>
+          <t>62618</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>84299</t>
+          <t>84312</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>167127</t>
+          <t>166283</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>199378</t>
+          <t>198791</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36649</t>
+          <t>36130</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34227</t>
+          <t>33518</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54357</t>
+          <t>54064</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21874</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28755</t>
+          <t>28857</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>26847</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45669</t>
+          <t>45225</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35342</t>
+          <t>34972</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>54619</t>
+          <t>55159</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>79991</t>
+          <t>80491</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>77845</t>
+          <t>77038</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>107932</t>
+          <t>107424</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>79200</t>
+          <t>79811</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>106613</t>
+          <t>107468</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>126659</t>
+          <t>126229</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>160479</t>
+          <t>160323</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>214033</t>
+          <t>213386</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>261775</t>
+          <t>258566</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>352060</t>
+          <t>353449</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>394220</t>
+          <t>394466</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>301371</t>
+          <t>301416</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>343686</t>
+          <t>343867</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>663499</t>
+          <t>667455</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>723313</t>
+          <t>728528</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>153497</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>189808</t>
+          <t>189953</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>151063</t>
+          <t>150375</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>188270</t>
+          <t>187450</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>313924</t>
+          <t>314300</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>366474</t>
+          <t>366319</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre en 2012 (tasa de respuesta: 98,95%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre en 2012 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13619</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9419</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21864</t>
+          <t>21573</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38061</t>
+          <t>38184</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55851</t>
+          <t>57333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33249</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50662</t>
+          <t>50127</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75442</t>
+          <t>75378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101105</t>
+          <t>101108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75688</t>
+          <t>74920</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93683</t>
+          <t>93752</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80872</t>
+          <t>81772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99085</t>
+          <t>100521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>161531</t>
+          <t>161292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188156</t>
+          <t>188485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,62%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19477</t>
+          <t>20310</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23582</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25728</t>
+          <t>25467</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43449</t>
+          <t>43127</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43653</t>
+          <t>43941</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66019</t>
+          <t>66305</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74613</t>
+          <t>74896</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>104470</t>
+          <t>103232</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155424</t>
+          <t>156161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178822</t>
+          <t>179020</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>171132</t>
+          <t>169019</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>195731</t>
+          <t>195919</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>333867</t>
+          <t>333579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>368170</t>
+          <t>368216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,48%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>37407</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23223</t>
+          <t>24136</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>33715</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54682</t>
+          <t>55758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>13378</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32371</t>
+          <t>32436</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>23889</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>42385</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33010</t>
+          <t>32150</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51473</t>
+          <t>51002</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55011</t>
+          <t>54914</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75406</t>
+          <t>76195</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92623</t>
+          <t>91794</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>122431</t>
+          <t>120731</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88798</t>
+          <t>88553</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>108795</t>
+          <t>108846</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55762</t>
+          <t>55397</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76296</t>
+          <t>76129</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>149340</t>
+          <t>150380</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178882</t>
+          <t>179549</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,3%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11292</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>14400</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30939</t>
+          <t>30353</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47840</t>
+          <t>48951</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37526</t>
+          <t>36505</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>57893</t>
+          <t>57488</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41748</t>
+          <t>42905</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62687</t>
+          <t>62392</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65966</t>
+          <t>65580</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>87823</t>
+          <t>87907</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>115227</t>
+          <t>114458</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>143251</t>
+          <t>144958</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>75859</t>
+          <t>75474</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>98158</t>
+          <t>96003</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44275</t>
+          <t>44491</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64002</t>
+          <t>65642</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125903</t>
+          <t>125717</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>156607</t>
+          <t>155692</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,32%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17879</t>
+          <t>18106</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32329</t>
+          <t>33809</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15869</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25109</t>
+          <t>26382</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43184</t>
+          <t>45861</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6509</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>11462</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24203</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30174</t>
+          <t>29384</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>61920</t>
+          <t>62524</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>89184</t>
+          <t>88747</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>81889</t>
+          <t>81145</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>112598</t>
+          <t>113189</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>115263</t>
+          <t>114813</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>149438</t>
+          <t>150442</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>177129</t>
+          <t>176498</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>216783</t>
+          <t>216435</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>302497</t>
+          <t>300942</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>355878</t>
+          <t>355377</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>378825</t>
+          <t>375876</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>423534</t>
+          <t>420823</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>324662</t>
+          <t>323154</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>366750</t>
+          <t>366976</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>711119</t>
+          <t>715918</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>777450</t>
+          <t>776651</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>126335</t>
+          <t>126031</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>161135</t>
+          <t>160032</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>101268</t>
+          <t>101381</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>134647</t>
+          <t>136456</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>238919</t>
+          <t>237913</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>285448</t>
+          <t>284186</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre en 2016 (tasa de respuesta: 99,62%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13327</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17650</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>34501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52631</t>
+          <t>51493</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30517</t>
+          <t>30172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>46171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70608</t>
+          <t>71160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93302</t>
+          <t>93211</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72995</t>
+          <t>73770</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90350</t>
+          <t>91475</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62266</t>
+          <t>62682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79596</t>
+          <t>79517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141054</t>
+          <t>142340</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165689</t>
+          <t>165739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,61%</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>26390</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20964</t>
+          <t>20901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36896</t>
+          <t>36615</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>36278</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55985</t>
+          <t>55789</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61197</t>
+          <t>60822</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87389</t>
+          <t>86479</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131185</t>
+          <t>131242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151395</t>
+          <t>152536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>152931</t>
+          <t>153019</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>177569</t>
+          <t>176374</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>290570</t>
+          <t>288958</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>322951</t>
+          <t>322875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>24211</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41704</t>
+          <t>41074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26482</t>
+          <t>25503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43309</t>
+          <t>43165</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54896</t>
+          <t>55774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79501</t>
+          <t>80074</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18372</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30144</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26447</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44606</t>
+          <t>44863</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31378</t>
+          <t>31342</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50336</t>
+          <t>49855</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49491</t>
+          <t>49757</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70902</t>
+          <t>70992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>87854</t>
+          <t>85734</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116535</t>
+          <t>113555</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>109989</t>
+          <t>110274</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131191</t>
+          <t>132013</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86580</t>
+          <t>85980</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109208</t>
+          <t>108624</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>201910</t>
+          <t>202761</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>233438</t>
+          <t>233849</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>9886</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22103</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12601</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>16026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31450</t>
+          <t>30911</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18599</t>
+          <t>17996</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20688</t>
+          <t>21602</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>37840</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31159</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51377</t>
+          <t>50930</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36306</t>
+          <t>34755</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54881</t>
+          <t>54732</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47392</t>
+          <t>46850</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>68238</t>
+          <t>67584</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>87714</t>
+          <t>87174</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>116549</t>
+          <t>116085</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>81090</t>
+          <t>80849</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102122</t>
+          <t>102551</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66311</t>
+          <t>65908</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88477</t>
+          <t>87747</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152684</t>
+          <t>152113</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>182635</t>
+          <t>183073</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>17291</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32922</t>
+          <t>32179</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26624</t>
+          <t>26976</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>46112</t>
+          <t>46537</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24104</t>
+          <t>24146</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41842</t>
+          <t>40783</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>50618</t>
+          <t>51044</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>75724</t>
+          <t>76538</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>79640</t>
+          <t>81353</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>110033</t>
+          <t>111763</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97764</t>
+          <t>98669</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>129761</t>
+          <t>129155</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>148413</t>
+          <t>147861</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>186263</t>
+          <t>186513</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>254627</t>
+          <t>255328</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>304513</t>
+          <t>305149</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>377563</t>
+          <t>377931</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>418649</t>
+          <t>419266</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>351445</t>
+          <t>356063</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>398442</t>
+          <t>400403</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>747219</t>
+          <t>741922</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>809419</t>
+          <t>803888</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>136754</t>
+          <t>136692</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>171778</t>
+          <t>172716</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>109816</t>
+          <t>108004</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>142331</t>
+          <t>139898</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>255880</t>
+          <t>255509</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>304123</t>
+          <t>302504</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre en 2023 (tasa de respuesta: 99,43%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre en 2023 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15606</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>855</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13640</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>14601</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26499</t>
+          <t>25909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31151</t>
+          <t>31762</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46797</t>
+          <t>46976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,0%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19685</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30899</t>
+          <t>30929</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36572</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48178</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64207</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,37%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17429</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>13012</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29562</t>
+          <t>28641</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27792</t>
+          <t>27655</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31967</t>
+          <t>31887</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52561</t>
+          <t>52471</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49576</t>
+          <t>50226</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74280</t>
+          <t>74083</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81752</t>
+          <t>81147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102975</t>
+          <t>101940</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80184</t>
+          <t>81218</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104309</t>
+          <t>104041</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169807</t>
+          <t>170225</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>201089</t>
+          <t>201278</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,96%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25431</t>
+          <t>25463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44444</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37532</t>
+          <t>38030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51960</t>
+          <t>50409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77869</t>
+          <t>75926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31388</t>
+          <t>30441</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>21554</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41125</t>
+          <t>42014</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37609</t>
+          <t>36886</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63531</t>
+          <t>61232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28983</t>
+          <t>28223</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47409</t>
+          <t>47092</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44727</t>
+          <t>45359</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71336</t>
+          <t>71111</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>80682</t>
+          <t>78359</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>111928</t>
+          <t>111284</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81136</t>
+          <t>82076</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105485</t>
+          <t>106422</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80337</t>
+          <t>80443</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108085</t>
+          <t>109943</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>169144</t>
+          <t>170045</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>206122</t>
+          <t>207049</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29431</t>
+          <t>29329</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20356</t>
+          <t>19460</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39389</t>
+          <t>39250</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38503</t>
+          <t>38591</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60905</t>
+          <t>63543</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17407</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34968</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40115</t>
+          <t>40332</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>67005</t>
+          <t>66242</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63239</t>
+          <t>63088</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>96592</t>
+          <t>96759</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45544</t>
+          <t>44958</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>80321</t>
+          <t>79986</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66504</t>
+          <t>68060</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103079</t>
+          <t>104768</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120761</t>
+          <t>120347</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>173594</t>
+          <t>172134</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74344</t>
+          <t>77093</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124537</t>
+          <t>125790</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97988</t>
+          <t>101042</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>137857</t>
+          <t>139455</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>190081</t>
+          <t>187545</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>253952</t>
+          <t>253515</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>48084</t>
+          <t>47751</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130892</t>
+          <t>135168</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33201</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>82439</t>
+          <t>79700</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>89224</t>
+          <t>90361</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>209379</t>
+          <t>200561</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>21777</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>19949</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>21064</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36834</t>
+          <t>37083</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>43971</t>
+          <t>44882</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>72726</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>79863</t>
+          <t>81121</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>118002</t>
+          <t>114773</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>131899</t>
+          <t>131762</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>175413</t>
+          <t>174382</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>103671</t>
+          <t>105673</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>143876</t>
+          <t>145262</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,47 +14628,47 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>21,88%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>184903</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>164197</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>211456</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
           <t>21,67%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>184903</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>160068</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>208894</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>277958</t>
+          <t>277124</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>340459</t>
+          <t>340671</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>267540</t>
+          <t>268662</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>338461</t>
+          <t>339342</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300735</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>354319</t>
+          <t>354232</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>592783</t>
+          <t>589720</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>677064</t>
+          <t>678934</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>125608</t>
+          <t>124635</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>237866</t>
+          <t>229313</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>116013</t>
+          <t>115769</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>169253</t>
+          <t>168429</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>252371</t>
+          <t>251372</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>368345</t>
+          <t>362673</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
